--- a/2024AIDataScienceGNRGeneral/Advanced Excel/dec28.xlsx
+++ b/2024AIDataScienceGNRGeneral/Advanced Excel/dec28.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D01B2-DBDE-48E3-99ED-F745A8A955B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4AB6B3-3CBB-49A8-9011-BF1E37FACA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AC0E3AFF-C2B3-4F6D-972A-E31AA2734485}"/>
   </bookViews>
@@ -536,11 +536,19 @@
       <c r="G2">
         <v>55</v>
       </c>
+      <c r="H2" t="str">
+        <f>IF(G2&gt;=70, "Yes", "No")</f>
+        <v>No</v>
+      </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
+      </c>
+      <c r="K2">
+        <f>IF(G2&gt;=70, E2+$F$2, E2)</f>
+        <v>74</v>
       </c>
       <c r="L2" s="1">
         <f>SUM(I2:I15)</f>
@@ -559,11 +567,19 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E15" si="1">D3+D$20</f>
+        <f t="shared" ref="E3:E13" si="1">D3+D$20</f>
         <v>51</v>
       </c>
       <c r="G3">
         <v>68</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H20" si="2">IF(G3&gt;=70, "Yes", "No")</f>
+        <v>No</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K15" si="3">IF(G3&gt;=70, E3+$F$2, E3)</f>
+        <v>51</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>14</v>
@@ -590,6 +606,14 @@
       <c r="G4">
         <v>77</v>
       </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>74</v>
+      </c>
       <c r="L4" s="1">
         <f>COUNT(C2:C15)</f>
         <v>11</v>
@@ -613,8 +637,16 @@
       <c r="G5">
         <v>98</v>
       </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="I5">
         <v>1</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>15</v>
@@ -641,11 +673,19 @@
       <c r="G6">
         <v>83</v>
       </c>
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
         <v>13</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>87</v>
       </c>
       <c r="L6" s="1">
         <f>COUNT(B2:B15)</f>
@@ -670,11 +710,19 @@
       <c r="G7">
         <v>92</v>
       </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
         <v>13</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>64</v>
       </c>
       <c r="L7" s="1"/>
     </row>
@@ -699,8 +747,16 @@
       <c r="G8">
         <v>52</v>
       </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
       <c r="I8">
         <v>1</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>61</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>16</v>
@@ -724,6 +780,14 @@
       <c r="G9">
         <v>33</v>
       </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
       <c r="L9" s="1">
         <f>COUNTA(J2:J15)</f>
         <v>8</v>
@@ -750,11 +814,19 @@
       <c r="G10">
         <v>8</v>
       </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>13</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>21</v>
@@ -781,6 +853,14 @@
       <c r="G11">
         <v>42</v>
       </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
       <c r="L11" s="1">
         <f>COUNTIF(G2:G15, "&gt;=70")</f>
         <v>6</v>
@@ -793,11 +873,19 @@
       <c r="G12">
         <v>49</v>
       </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
         <v>13</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>22</v>
@@ -824,8 +912,16 @@
       <c r="G13">
         <v>39</v>
       </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>No</v>
+      </c>
       <c r="J13" t="s">
         <v>13</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>71</v>
       </c>
       <c r="L13" s="2">
         <f>COUNTIF(G2:G15, 8)</f>
@@ -850,11 +946,19 @@
       <c r="G14">
         <v>90</v>
       </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
         <v>13</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>17</v>
@@ -881,11 +985,19 @@
       <c r="G15">
         <v>80</v>
       </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>Yes</v>
+      </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="J15" t="s">
         <v>13</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="L15" s="1">
         <f>COUNTIFS(B2:B15, "&gt;=25", C2:C15, "&lt;=20")</f>
